--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T20:24:08+00:00</t>
+    <t>2026-10-19T15:55:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T15:55:36+00:00</t>
+    <t>2026-10-19T16:11:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T16:11:48+00:00</t>
+    <t>2026-10-19T18:28:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T18:28:35+00:00</t>
+    <t>2026-10-20T08:04:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T08:04:36+00:00</t>
+    <t>2026-10-20T12:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T12:30:11+00:00</t>
+    <t>2026-10-20T15:36:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T15:36:59+00:00</t>
+    <t>2026-10-20T16:38:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T16:38:16+00:00</t>
+    <t>2026-10-20T17:05:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T17:05:58+00:00</t>
+    <t>2026-10-21T09:29:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:29:04+00:00</t>
+    <t>2026-10-21T09:52:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:52:38+00:00</t>
+    <t>2026-10-21T10:08:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T10:08:52+00:00</t>
+    <t>2026-10-21T11:24:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T11:24:22+00:00</t>
+    <t>2026-10-21T12:17:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T12:17:05+00:00</t>
+    <t>2026-10-21T14:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T14:17:59+00:00</t>
+    <t>2026-10-21T15:07:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:07:55+00:00</t>
+    <t>2026-10-21T15:51:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:51:37+00:00</t>
+    <t>2026-10-22T07:17:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:17:51+00:00</t>
+    <t>2026-10-22T07:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:44:55+00:00</t>
+    <t>2026-10-22T08:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T08:46:49+00:00</t>
+    <t>2026-10-22T09:37:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:37:30+00:00</t>
+    <t>2026-10-22T09:48:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:48:24+00:00</t>
+    <t>2026-10-22T11:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T11:28:40+00:00</t>
+    <t>2026-10-22T12:03:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:03:52+00:00</t>
+    <t>2026-10-22T12:14:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:14:48+00:00</t>
+    <t>2026-10-22T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T18:22:51+00:00</t>
+    <t>2026-10-23T11:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T11:54:03+00:00</t>
+    <t>2026-10-23T12:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T12:23:07+00:00</t>
+    <t>2026-10-23T13:54:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T13:54:21+00:00</t>
+    <t>2026-10-23T16:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T16:16:05+00:00</t>
+    <t>2026-10-26T11:42:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T11:42:48+00:00</t>
+    <t>2026-10-26T12:04:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T12:04:07+00:00</t>
+    <t>2026-10-26T13:41:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:41:17+00:00</t>
+    <t>2026-10-26T13:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:57:36+00:00</t>
+    <t>2026-10-26T16:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:01:21+00:00</t>
+    <t>2026-10-26T16:19:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:19:19+00:00</t>
+    <t>2026-10-26T17:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:11:45+00:00</t>
+    <t>2026-10-26T17:20:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:20:41+00:00</t>
+    <t>2026-10-26T17:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:56:13+00:00</t>
+    <t>2026-10-26T18:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T18:36:30+00:00</t>
+    <t>2026-10-26T20:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:24:37+00:00</t>
+    <t>2026-10-26T20:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:58:24+00:00</t>
+    <t>2026-10-26T21:10:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T21:10:14+00:00</t>
+    <t>2026-10-27T12:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:33:12+00:00</t>
+    <t>2026-10-27T12:53:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:53:20+00:00</t>
+    <t>2026-10-27T13:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T13:46:50+00:00</t>
+    <t>2026-10-27T19:38:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T19:38:06+00:00</t>
+    <t>2026-10-27T20:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T20:05:18+00:00</t>
+    <t>2026-10-27T21:19:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T21:19:55+00:00</t>
+    <t>2026-10-28T09:21:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T09:21:39+00:00</t>
+    <t>2026-10-28T10:28:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T10:28:56+00:00</t>
+    <t>2026-10-28T15:47:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T15:47:56+00:00</t>
+    <t>2026-10-28T21:33:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T21:33:03+00:00</t>
+    <t>2026-10-29T07:35:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:35:42+00:00</t>
+    <t>2026-10-29T08:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:12:50+00:00</t>
+    <t>2026-10-29T08:46:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:46:29+00:00</t>
+    <t>2026-10-29T10:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:03:24+00:00</t>
+    <t>2026-10-29T10:46:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:46:22+00:00</t>
+    <t>2026-10-29T11:16:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T11:16:49+00:00</t>
+    <t>2026-10-29T12:53:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-medicationdispense-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T12:53:50+00:00</t>
+    <t>2026-10-29T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
